--- a/data/result3.xlsx
+++ b/data/result3.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="libxl" lastEdited="7" lowestEdited="6" rupBuild="4.6.0"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C236CD6-1B49-404B-932D-9472C56F736E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="61" uniqueCount="22">
   <si>
     <t>无人机编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -100,13 +100,25 @@
   <si>
     <t>FY5</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烟幕干扰弹投放点的z 坐标 (m)</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,7 +143,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -139,25 +151,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -176,7 +190,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -327,7 +341,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -351,9 +365,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -377,7 +391,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -412,7 +426,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -430,7 +444,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -455,7 +469,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -491,17 +505,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.58203125" customWidth="1"/>
-    <col min="2" max="4" width="16.58203125" customWidth="1"/>
-    <col min="5" max="11" width="14.58203125" customWidth="1"/>
-    <col min="12" max="12" width="16.58203125" customWidth="1"/>
+    <col min="1" max="1" width="10.08203125" customWidth="true"/>
+    <col min="2" max="2" width="13.75" customWidth="true"/>
+    <col min="5" max="5" width="25" customWidth="true"/>
+    <col min="12" max="12" width="13.75" customWidth="true"/>
+    <col min="3" max="3" width="18.25" customWidth="true"/>
+    <col min="4" max="4" width="13.75" customWidth="true"/>
+    <col min="6" max="6" width="25" customWidth="true"/>
+    <col min="7" max="7" width="25.5" customWidth="true"/>
+    <col min="8" max="8" width="25" customWidth="true"/>
+    <col min="9" max="9" width="25" customWidth="true"/>
+    <col min="10" max="10" width="25" customWidth="true"/>
+    <col min="11" max="11" width="14.1640625" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" s="2" customFormat="true" ht="28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,7 +543,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
@@ -539,131 +561,405 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="B2" s="0">
+        <v>10</v>
+      </c>
+      <c r="C2" s="0">
+        <v>110</v>
+      </c>
       <c r="D2" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E2" s="0">
+        <v>17800</v>
+      </c>
+      <c r="F2" s="0">
+        <v>0</v>
+      </c>
+      <c r="G2" s="0">
+        <v>1800</v>
+      </c>
+      <c r="H2" s="0">
+        <v>17854.164426415671</v>
+      </c>
+      <c r="I2" s="0">
+        <v>9.5506497716811687</v>
+      </c>
+      <c r="J2" s="0">
+        <v>1798.7750000000001</v>
+      </c>
+      <c r="K2" s="0">
+        <v>4.5049999999999999</v>
+      </c>
+      <c r="L2" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="B3" s="0"/>
+      <c r="C3" s="0"/>
       <c r="D3" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+      <c r="I3" s="0"/>
+      <c r="J3" s="0"/>
+      <c r="K3" s="0"/>
+      <c r="L3" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="B4" s="0"/>
+      <c r="C4" s="0"/>
       <c r="D4" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E4" s="0"/>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
+      <c r="I4" s="0"/>
+      <c r="J4" s="0"/>
+      <c r="K4" s="0"/>
+      <c r="L4" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="B5" s="0">
+        <v>270</v>
+      </c>
+      <c r="C5" s="0">
+        <v>130</v>
+      </c>
       <c r="D5" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E5" s="0">
+        <v>12000</v>
+      </c>
+      <c r="F5" s="0">
+        <v>879.99999999999989</v>
+      </c>
+      <c r="G5" s="0">
+        <v>1400</v>
+      </c>
+      <c r="H5" s="0">
+        <v>12000</v>
+      </c>
+      <c r="I5" s="0">
+        <v>424.99999999999989</v>
+      </c>
+      <c r="J5" s="0">
+        <v>1339.9749999999999</v>
+      </c>
+      <c r="K5" s="0">
+        <v>3.875</v>
+      </c>
+      <c r="L5" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="B6" s="0"/>
+      <c r="C6" s="0"/>
       <c r="D6" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E6" s="0"/>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
+      <c r="I6" s="0"/>
+      <c r="J6" s="0"/>
+      <c r="K6" s="0"/>
+      <c r="L6" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="B7" s="0"/>
+      <c r="C7" s="0"/>
       <c r="D7" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
+      <c r="I7" s="0"/>
+      <c r="J7" s="0"/>
+      <c r="K7" s="0"/>
+      <c r="L7" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="B8" s="0">
+        <v>100</v>
+      </c>
+      <c r="C8" s="0">
+        <v>120</v>
+      </c>
       <c r="D8" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E8" s="0">
+        <v>5584.0547294665603</v>
+      </c>
+      <c r="F8" s="0">
+        <v>-641.05714926773499</v>
+      </c>
+      <c r="G8" s="0">
+        <v>700</v>
+      </c>
+      <c r="H8" s="0">
+        <v>5490.2847135264183</v>
+      </c>
+      <c r="I8" s="0">
+        <v>-109.26096264114267</v>
+      </c>
+      <c r="J8" s="0">
+        <v>600.77499999999998</v>
+      </c>
+      <c r="K8" s="0">
+        <v>2.6400000000000001</v>
+      </c>
+      <c r="L8" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="B9" s="0"/>
+      <c r="C9" s="0"/>
       <c r="D9" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
+      <c r="I9" s="0"/>
+      <c r="J9" s="0"/>
+      <c r="K9" s="0"/>
+      <c r="L9" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
       <c r="D10" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E10" s="0"/>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
+      <c r="I10" s="0"/>
+      <c r="J10" s="0"/>
+      <c r="K10" s="0"/>
+      <c r="L10" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="B11" s="0">
+        <v>280</v>
+      </c>
+      <c r="C11" s="0">
+        <v>130</v>
+      </c>
       <c r="D11" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E11" s="0">
+        <v>11045.148526193401</v>
+      </c>
+      <c r="F11" s="0">
+        <v>1743.9499842168259</v>
+      </c>
+      <c r="G11" s="0">
+        <v>1800</v>
+      </c>
+      <c r="H11" s="0">
+        <v>11282.178288708761</v>
+      </c>
+      <c r="I11" s="0">
+        <v>399.68740135516191</v>
+      </c>
+      <c r="J11" s="0">
+        <v>1259.7750000000001</v>
+      </c>
+      <c r="K11" s="0">
+        <v>3.605</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="B12" s="0"/>
+      <c r="C12" s="0"/>
       <c r="D12" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+      <c r="I12" s="0"/>
+      <c r="J12" s="0"/>
+      <c r="K12" s="0"/>
+      <c r="L12" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="B13" s="0"/>
+      <c r="C13" s="0"/>
       <c r="D13" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E13" s="0"/>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
+      <c r="I13" s="0"/>
+      <c r="J13" s="0"/>
+      <c r="K13" s="0"/>
+      <c r="L13" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="B14" s="0">
+        <v>110</v>
+      </c>
+      <c r="C14" s="0">
+        <v>110</v>
+      </c>
       <c r="D14" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E14" s="0">
+        <v>12398.044547746824</v>
+      </c>
+      <c r="F14" s="0">
+        <v>-346.14098741680118</v>
+      </c>
+      <c r="G14" s="0">
+        <v>1300</v>
+      </c>
+      <c r="H14" s="0">
+        <v>12266.366792566441</v>
+      </c>
+      <c r="I14" s="0">
+        <v>15.640671585773589</v>
+      </c>
+      <c r="J14" s="0">
+        <v>1239.9749999999999</v>
+      </c>
+      <c r="K14" s="0">
+        <v>3.4250000000000003</v>
+      </c>
+      <c r="L14" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="B15" s="0"/>
+      <c r="C15" s="0"/>
       <c r="D15" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E15" s="0"/>
+      <c r="F15" s="0"/>
+      <c r="G15" s="0"/>
+      <c r="H15" s="0"/>
+      <c r="I15" s="0"/>
+      <c r="J15" s="0"/>
+      <c r="K15" s="0"/>
+      <c r="L15" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="B16" s="0"/>
+      <c r="C16" s="0"/>
       <c r="D16" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+      <c r="I16" s="0"/>
+      <c r="J16" s="0"/>
+      <c r="K16" s="0"/>
+      <c r="L16" s="0"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+      <c r="C17" s="0"/>
+      <c r="D17" s="0"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0"/>
+      <c r="G17" s="0"/>
+      <c r="H17" s="0"/>
+      <c r="I17" s="0"/>
+      <c r="J17" s="0"/>
+      <c r="K17" s="0"/>
+      <c r="L17" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" ht="60" customHeight="true" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="C18" s="0"/>
+      <c r="D18" s="0"/>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0"/>
+      <c r="G18" s="0"/>
+      <c r="H18" s="0"/>
+      <c r="I18" s="0"/>
+      <c r="J18" s="0"/>
+      <c r="K18" s="0"/>
+      <c r="L18" s="0"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/result3.xlsx
+++ b/data/result3.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="61" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="128" uniqueCount="22">
   <si>
     <t>无人机编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -566,10 +566,10 @@
         <v>13</v>
       </c>
       <c r="B2" s="0">
-        <v>10</v>
+        <v>6.9549885439956949</v>
       </c>
       <c r="C2" s="0">
-        <v>110</v>
+        <v>106.77615554527519</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -584,16 +584,16 @@
         <v>1800</v>
       </c>
       <c r="H2" s="0">
-        <v>17854.164426415671</v>
+        <v>17852.484955318556</v>
       </c>
       <c r="I2" s="0">
-        <v>9.5506497716811687</v>
+        <v>6.4024925225033833</v>
       </c>
       <c r="J2" s="0">
-        <v>1798.7750000000001</v>
+        <v>1798.7984765471672</v>
       </c>
       <c r="K2" s="0">
-        <v>4.5049999999999999</v>
+        <v>4.3650000000000002</v>
       </c>
       <c r="L2" s="0" t="s">
         <v>19</v>
@@ -603,19 +603,39 @@
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="0"/>
-      <c r="C3" s="0"/>
+      <c r="B3" s="0">
+        <v>6.9549885439956949</v>
+      </c>
+      <c r="C3" s="0">
+        <v>106.77615554527519</v>
+      </c>
       <c r="D3" s="3">
         <v>2</v>
       </c>
-      <c r="E3" s="0"/>
-      <c r="F3" s="0"/>
-      <c r="G3" s="0"/>
-      <c r="H3" s="0"/>
-      <c r="I3" s="0"/>
-      <c r="J3" s="0"/>
-      <c r="K3" s="0"/>
-      <c r="L3" s="0"/>
+      <c r="E3" s="0">
+        <v>17905.990452352751</v>
+      </c>
+      <c r="F3" s="0">
+        <v>12.929478067123979</v>
+      </c>
+      <c r="G3" s="0">
+        <v>1800</v>
+      </c>
+      <c r="H3" s="0">
+        <v>17911.365398785016</v>
+      </c>
+      <c r="I3" s="0">
+        <v>13.585152710125078</v>
+      </c>
+      <c r="J3" s="0">
+        <v>1799.9873988300349</v>
+      </c>
+      <c r="K3" s="0">
+        <v>4.3950000000000005</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -652,7 +672,7 @@
         <v>12000</v>
       </c>
       <c r="F5" s="0">
-        <v>879.99999999999989</v>
+        <v>880</v>
       </c>
       <c r="G5" s="0">
         <v>1400</v>
@@ -661,7 +681,7 @@
         <v>12000</v>
       </c>
       <c r="I5" s="0">
-        <v>424.99999999999989</v>
+        <v>425</v>
       </c>
       <c r="J5" s="0">
         <v>1339.9749999999999</v>
@@ -714,7 +734,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="0">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C8" s="0">
         <v>120</v>
@@ -723,28 +743,28 @@
         <v>1</v>
       </c>
       <c r="E8" s="0">
-        <v>5584.0547294665603</v>
+        <v>6000</v>
       </c>
       <c r="F8" s="0">
-        <v>-641.05714926773499</v>
+        <v>-360</v>
       </c>
       <c r="G8" s="0">
         <v>700</v>
       </c>
       <c r="H8" s="0">
-        <v>5490.2847135264183</v>
+        <v>6000</v>
       </c>
       <c r="I8" s="0">
-        <v>-109.26096264114267</v>
+        <v>60</v>
       </c>
       <c r="J8" s="0">
-        <v>600.77499999999998</v>
+        <v>639.97500000000002</v>
       </c>
       <c r="K8" s="0">
-        <v>2.6400000000000001</v>
+        <v>2.6299999999999999</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.3">
@@ -862,37 +882,37 @@
         <v>17</v>
       </c>
       <c r="B14" s="0">
-        <v>110</v>
+        <v>115.3943710092633</v>
       </c>
       <c r="C14" s="0">
-        <v>110</v>
+        <v>133.78382740889123</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
       </c>
       <c r="E14" s="0">
-        <v>12398.044547746824</v>
+        <v>12243.845000988271</v>
       </c>
       <c r="F14" s="0">
-        <v>-346.14098741680118</v>
+        <v>-407.13741582123157</v>
       </c>
       <c r="G14" s="0">
         <v>1300</v>
       </c>
       <c r="H14" s="0">
-        <v>12266.366792566441</v>
+        <v>12237.235869359442</v>
       </c>
       <c r="I14" s="0">
-        <v>15.640671585773589</v>
+        <v>-393.21508706689701</v>
       </c>
       <c r="J14" s="0">
-        <v>1239.9749999999999</v>
+        <v>1299.9349759305726</v>
       </c>
       <c r="K14" s="0">
-        <v>3.4250000000000003</v>
+        <v>3.7050000000000001</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.3">

--- a/data/result3.xlsx
+++ b/data/result3.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="128" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="165" uniqueCount="22">
   <si>
     <t>无人机编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -566,10 +566,10 @@
         <v>13</v>
       </c>
       <c r="B2" s="0">
-        <v>6.9549885439956949</v>
+        <v>10</v>
       </c>
       <c r="C2" s="0">
-        <v>106.77615554527519</v>
+        <v>98.847462386448854</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -584,16 +584,16 @@
         <v>1800</v>
       </c>
       <c r="H2" s="0">
-        <v>17852.484955318556</v>
+        <v>17813.973046085757</v>
       </c>
       <c r="I2" s="0">
-        <v>6.4024925225033833</v>
+        <v>2.4638250276019518</v>
       </c>
       <c r="J2" s="0">
-        <v>1798.7984765471672</v>
+        <v>1799.8990411730513</v>
       </c>
       <c r="K2" s="0">
-        <v>4.3650000000000002</v>
+        <v>3.1400000000000001</v>
       </c>
       <c r="L2" s="0" t="s">
         <v>19</v>
@@ -604,34 +604,34 @@
         <v>13</v>
       </c>
       <c r="B3" s="0">
-        <v>6.9549885439956949</v>
+        <v>10</v>
       </c>
       <c r="C3" s="0">
-        <v>106.77615554527519</v>
+        <v>98.847462386448854</v>
       </c>
       <c r="D3" s="3">
         <v>2</v>
       </c>
       <c r="E3" s="0">
-        <v>17905.990452352751</v>
+        <v>17897.345747323758</v>
       </c>
       <c r="F3" s="0">
-        <v>12.929478067123979</v>
+        <v>17.164681710407283</v>
       </c>
       <c r="G3" s="0">
         <v>1800</v>
       </c>
       <c r="H3" s="0">
-        <v>17911.365398785016</v>
+        <v>17901.597340871955</v>
       </c>
       <c r="I3" s="0">
-        <v>13.585152710125078</v>
+        <v>17.914352363960578</v>
       </c>
       <c r="J3" s="0">
-        <v>1799.9873988300349</v>
+        <v>1799.9906531431452</v>
       </c>
       <c r="K3" s="0">
-        <v>4.3950000000000005</v>
+        <v>3.4100000000000001</v>
       </c>
       <c r="L3" s="0" t="s">
         <v>19</v>
@@ -663,7 +663,7 @@
         <v>270</v>
       </c>
       <c r="C5" s="0">
-        <v>130</v>
+        <v>128.50411176738831</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -672,7 +672,7 @@
         <v>12000</v>
       </c>
       <c r="F5" s="0">
-        <v>880</v>
+        <v>885.98355293044676</v>
       </c>
       <c r="G5" s="0">
         <v>1400</v>
@@ -681,13 +681,13 @@
         <v>12000</v>
       </c>
       <c r="I5" s="0">
-        <v>425</v>
+        <v>427.7303382721887</v>
       </c>
       <c r="J5" s="0">
-        <v>1339.9749999999999</v>
+        <v>1337.6878017843599</v>
       </c>
       <c r="K5" s="0">
-        <v>3.875</v>
+        <v>3.8650000000000002</v>
       </c>
       <c r="L5" s="0" t="s">
         <v>20</v>
@@ -697,37 +697,77 @@
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="0"/>
-      <c r="C6" s="0"/>
+      <c r="B6" s="0">
+        <v>270</v>
+      </c>
+      <c r="C6" s="0">
+        <v>128.50411176738831</v>
+      </c>
       <c r="D6" s="3">
         <v>2</v>
       </c>
-      <c r="E6" s="0"/>
-      <c r="F6" s="0"/>
-      <c r="G6" s="0"/>
-      <c r="H6" s="0"/>
-      <c r="I6" s="0"/>
-      <c r="J6" s="0"/>
-      <c r="K6" s="0"/>
-      <c r="L6" s="0"/>
+      <c r="E6" s="0">
+        <v>12000</v>
+      </c>
+      <c r="F6" s="0">
+        <v>757.47944116305848</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1400</v>
+      </c>
+      <c r="H6" s="0">
+        <v>12000</v>
+      </c>
+      <c r="I6" s="0">
+        <v>395.94769313361667</v>
+      </c>
+      <c r="J6" s="0">
+        <v>1361.2157931949644</v>
+      </c>
+      <c r="K6" s="0">
+        <v>3.6499999999999999</v>
+      </c>
+      <c r="L6" s="0" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0"/>
-      <c r="C7" s="0"/>
+      <c r="B7" s="0">
+        <v>270</v>
+      </c>
+      <c r="C7" s="0">
+        <v>128.50411176738831</v>
+      </c>
       <c r="D7" s="3">
         <v>3</v>
       </c>
-      <c r="E7" s="0"/>
-      <c r="F7" s="0"/>
-      <c r="G7" s="0"/>
-      <c r="H7" s="0"/>
-      <c r="I7" s="0"/>
-      <c r="J7" s="0"/>
-      <c r="K7" s="0"/>
-      <c r="L7" s="0"/>
+      <c r="E7" s="0">
+        <v>12000</v>
+      </c>
+      <c r="F7" s="0">
+        <v>628.97532939567009</v>
+      </c>
+      <c r="G7" s="0">
+        <v>1400</v>
+      </c>
+      <c r="H7" s="0">
+        <v>12000</v>
+      </c>
+      <c r="I7" s="0">
+        <v>376.67313916732132</v>
+      </c>
+      <c r="J7" s="0">
+        <v>1381.1112128333512</v>
+      </c>
+      <c r="K7" s="0">
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="L7" s="0" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -882,34 +922,34 @@
         <v>17</v>
       </c>
       <c r="B14" s="0">
-        <v>115.3943710092633</v>
+        <v>120</v>
       </c>
       <c r="C14" s="0">
-        <v>133.78382740889123</v>
+        <v>115.68714226171618</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
       </c>
       <c r="E14" s="0">
-        <v>12243.845000988271</v>
+        <v>12190.190004167987</v>
       </c>
       <c r="F14" s="0">
-        <v>-407.13741582123157</v>
+        <v>-597.36794274181239</v>
       </c>
       <c r="G14" s="0">
         <v>1300</v>
       </c>
       <c r="H14" s="0">
-        <v>12237.235869359442</v>
+        <v>12072.08756199816</v>
       </c>
       <c r="I14" s="0">
-        <v>-393.21508706689701</v>
+        <v>-392.80851240570621</v>
       </c>
       <c r="J14" s="0">
-        <v>1299.9349759305726</v>
+        <v>1279.5730445591803</v>
       </c>
       <c r="K14" s="0">
-        <v>3.7050000000000001</v>
+        <v>3.585</v>
       </c>
       <c r="L14" s="0" t="s">
         <v>21</v>
@@ -919,19 +959,39 @@
       <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="0"/>
-      <c r="C15" s="0"/>
+      <c r="B15" s="0">
+        <v>120</v>
+      </c>
+      <c r="C15" s="0">
+        <v>115.68714226171618</v>
+      </c>
       <c r="D15" s="3">
         <v>2</v>
       </c>
-      <c r="E15" s="0"/>
-      <c r="F15" s="0"/>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
-      <c r="I15" s="0"/>
-      <c r="J15" s="0"/>
-      <c r="K15" s="0"/>
-      <c r="L15" s="0"/>
+      <c r="E15" s="0">
+        <v>12132.346433037128</v>
+      </c>
+      <c r="F15" s="0">
+        <v>-497.17993865194194</v>
+      </c>
+      <c r="G15" s="0">
+        <v>1300</v>
+      </c>
+      <c r="H15" s="0">
+        <v>12078.469153069396</v>
+      </c>
+      <c r="I15" s="0">
+        <v>-403.86175237421679</v>
+      </c>
+      <c r="J15" s="0">
+        <v>1295.7489402517979</v>
+      </c>
+      <c r="K15" s="0">
+        <v>0.26000000000000001</v>
+      </c>
+      <c r="L15" s="0" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">

--- a/data/result3.xlsx
+++ b/data/result3.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="165" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="201" uniqueCount="22">
   <si>
     <t>无人机编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -663,7 +663,7 @@
         <v>270</v>
       </c>
       <c r="C5" s="0">
-        <v>128.50411176738831</v>
+        <v>128.58068871258772</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -672,7 +672,7 @@
         <v>12000</v>
       </c>
       <c r="F5" s="0">
-        <v>885.98355293044676</v>
+        <v>885.67724514964914</v>
       </c>
       <c r="G5" s="0">
         <v>1400</v>
@@ -681,13 +681,13 @@
         <v>12000</v>
       </c>
       <c r="I5" s="0">
-        <v>427.7303382721887</v>
+        <v>427.58576820508262</v>
       </c>
       <c r="J5" s="0">
-        <v>1337.6878017843599</v>
+        <v>1337.8059257380321</v>
       </c>
       <c r="K5" s="0">
-        <v>3.8650000000000002</v>
+        <v>3.8700000000000001</v>
       </c>
       <c r="L5" s="0" t="s">
         <v>20</v>
@@ -701,7 +701,7 @@
         <v>270</v>
       </c>
       <c r="C6" s="0">
-        <v>128.50411176738831</v>
+        <v>128.58068871258772</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -710,7 +710,7 @@
         <v>12000</v>
       </c>
       <c r="F6" s="0">
-        <v>757.47944116305848</v>
+        <v>757.09655643706139</v>
       </c>
       <c r="G6" s="0">
         <v>1400</v>
@@ -719,13 +719,13 @@
         <v>12000</v>
       </c>
       <c r="I6" s="0">
-        <v>395.94769313361667</v>
+        <v>395.19609202486009</v>
       </c>
       <c r="J6" s="0">
-        <v>1361.2157931949644</v>
+        <v>1361.1829197347643</v>
       </c>
       <c r="K6" s="0">
-        <v>3.6499999999999999</v>
+        <v>3.6299999999999999</v>
       </c>
       <c r="L6" s="0" t="s">
         <v>20</v>
@@ -735,39 +735,19 @@
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0">
-        <v>270</v>
-      </c>
-      <c r="C7" s="0">
-        <v>128.50411176738831</v>
-      </c>
+      <c r="B7" s="0"/>
+      <c r="C7" s="0"/>
       <c r="D7" s="3">
         <v>3</v>
       </c>
-      <c r="E7" s="0">
-        <v>12000</v>
-      </c>
-      <c r="F7" s="0">
-        <v>628.97532939567009</v>
-      </c>
-      <c r="G7" s="0">
-        <v>1400</v>
-      </c>
-      <c r="H7" s="0">
-        <v>12000</v>
-      </c>
-      <c r="I7" s="0">
-        <v>376.67313916732132</v>
-      </c>
-      <c r="J7" s="0">
-        <v>1381.1112128333512</v>
-      </c>
-      <c r="K7" s="0">
-        <v>0.35000000000000003</v>
-      </c>
-      <c r="L7" s="0" t="s">
-        <v>20</v>
-      </c>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
+      <c r="I7" s="0"/>
+      <c r="J7" s="0"/>
+      <c r="K7" s="0"/>
+      <c r="L7" s="0"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -777,7 +757,7 @@
         <v>90</v>
       </c>
       <c r="C8" s="0">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -786,7 +766,7 @@
         <v>6000</v>
       </c>
       <c r="F8" s="0">
-        <v>-360</v>
+        <v>0</v>
       </c>
       <c r="G8" s="0">
         <v>700</v>
@@ -795,16 +775,16 @@
         <v>6000</v>
       </c>
       <c r="I8" s="0">
-        <v>60</v>
+        <v>250.87174918565572</v>
       </c>
       <c r="J8" s="0">
-        <v>639.97500000000002</v>
+        <v>669.16104907565943</v>
       </c>
       <c r="K8" s="0">
-        <v>2.6299999999999999</v>
+        <v>2.6099999999999999</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.3">
